--- a/data/trans_dic/P2A_psíq_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_psíq_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica</t>
+          <t>Hogares con personas con limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,57</t>
+          <t>0,27; 1,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,25</t>
+          <t>1,5; 4,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,97</t>
+          <t>0,45; 2,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,12</t>
+          <t>0,58; 2,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,16</t>
+          <t>0,14; 1,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,69</t>
+          <t>1,92; 4,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,24</t>
+          <t>0,55; 2,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,54</t>
+          <t>1,61; 3,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,12</t>
+          <t>0,27; 1,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,84</t>
+          <t>2,0; 3,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,82</t>
+          <t>0,63; 1,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,56</t>
+          <t>1,33; 2,54</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,1</t>
+          <t>0,63; 2,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,57</t>
+          <t>0,9; 2,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,25</t>
+          <t>0,61; 2,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,32</t>
+          <t>0,7; 2,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,07</t>
+          <t>0,57; 2,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,84</t>
+          <t>1,05; 2,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,6</t>
+          <t>0,9; 2,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,6</t>
+          <t>2,01; 3,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,78</t>
+          <t>0,74; 1,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,36</t>
+          <t>1,16; 2,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,11</t>
+          <t>0,92; 2,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,71</t>
+          <t>1,31; 2,68</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,48</t>
+          <t>0,14; 1,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,22</t>
+          <t>0,52; 2,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,61</t>
+          <t>0,19; 1,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,76</t>
+          <t>1,93; 4,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,26</t>
+          <t>1,05; 3,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,17</t>
+          <t>0,52; 2,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,14</t>
+          <t>0,4; 2,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 56,95</t>
+          <t>2,55; 61,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,04</t>
+          <t>0,72; 2,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,85</t>
+          <t>0,66; 1,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,51</t>
+          <t>0,44; 1,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 42,98</t>
+          <t>2,7; 41,64</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,84</t>
+          <t>0,45; 1,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,66</t>
+          <t>1,37; 3,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,53</t>
+          <t>0,31; 1,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,51</t>
+          <t>1,96; 4,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,01</t>
+          <t>0,65; 2,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,63</t>
+          <t>1,6; 3,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,43</t>
+          <t>1,46; 3,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,16</t>
+          <t>2,19; 4,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,61</t>
+          <t>0,72; 1,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,14</t>
+          <t>1,7; 3,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,18</t>
+          <t>1,08; 2,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,93</t>
+          <t>2,21; 3,85</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,28</t>
+          <t>0,61; 1,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,38</t>
+          <t>1,42; 2,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,35</t>
+          <t>0,62; 1,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,78</t>
+          <t>1,54; 2,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,59</t>
+          <t>0,84; 1,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,67</t>
+          <t>1,67; 2,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,1</t>
+          <t>1,21; 2,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,67; 25,54</t>
+          <t>2,69; 25,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,31</t>
+          <t>0,82; 1,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,35</t>
+          <t>1,63; 2,33</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,58</t>
+          <t>1,03; 1,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,33; 15,07</t>
+          <t>2,35; 14,49</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica</t>
+          <t>Hogares con personas con limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1826; 10875</t>
+          <t>1853; 11044</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10626; 29904</t>
+          <t>10579; 29592</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2853; 13308</t>
+          <t>3026; 13941</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3374; 13497</t>
+          <t>3689; 13945</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>950; 7996</t>
+          <t>948; 8886</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13782; 32691</t>
+          <t>13379; 32029</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3788; 15092</t>
+          <t>3697; 14883</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11774; 25675</t>
+          <t>11643; 25633</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3910; 15484</t>
+          <t>3785; 14739</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26665; 53779</t>
+          <t>27972; 54401</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8560; 24477</t>
+          <t>8458; 24410</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17457; 34839</t>
+          <t>18079; 34608</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5564; 20242</t>
+          <t>6101; 21018</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9215; 26185</t>
+          <t>9137; 26623</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6893; 23021</t>
+          <t>6205; 23771</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7912; 27714</t>
+          <t>8406; 28129</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5510; 20066</t>
+          <t>5528; 19579</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10966; 29357</t>
+          <t>10867; 28976</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9266; 27098</t>
+          <t>9391; 28299</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19169; 34480</t>
+          <t>19235; 34534</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14937; 34345</t>
+          <t>14317; 34870</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24609; 48475</t>
+          <t>23810; 47446</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19540; 43562</t>
+          <t>18902; 42576</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29639; 58358</t>
+          <t>28179; 57613</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>987; 10026</t>
+          <t>980; 10405</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3063; 16803</t>
+          <t>3926; 19133</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1063; 12214</t>
+          <t>1409; 11241</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13487; 33534</t>
+          <t>13584; 33324</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7446; 22307</t>
+          <t>7213; 21765</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4946; 16857</t>
+          <t>4056; 16326</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3896; 16770</t>
+          <t>3129; 16846</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24280; 531579</t>
+          <t>23834; 570813</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9934; 27749</t>
+          <t>9836; 27629</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10349; 28462</t>
+          <t>10097; 28084</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7159; 23279</t>
+          <t>6790; 23656</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>45372; 704076</t>
+          <t>44171; 682057</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4120; 17293</t>
+          <t>4196; 18553</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13468; 34672</t>
+          <t>12952; 33119</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2870; 14321</t>
+          <t>2893; 13511</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17198; 41823</t>
+          <t>18158; 42702</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6130; 20872</t>
+          <t>6725; 21015</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16133; 38147</t>
+          <t>16837; 38240</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14911; 35750</t>
+          <t>15218; 36106</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23460; 45596</t>
+          <t>23956; 45527</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13390; 31861</t>
+          <t>14186; 33568</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33778; 62863</t>
+          <t>33902; 62505</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20494; 43230</t>
+          <t>21439; 44669</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>46152; 79429</t>
+          <t>44668; 77759</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19763; 41995</t>
+          <t>20150; 42995</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>46068; 81624</t>
+          <t>48781; 85110</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22447; 45701</t>
+          <t>21114; 46130</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55572; 96163</t>
+          <t>53415; 92622</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>28622; 53787</t>
+          <t>28386; 53962</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58274; 95142</t>
+          <t>59306; 92986</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43518; 74307</t>
+          <t>42883; 74139</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>99266; 948285</t>
+          <t>99799; 932453</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>53688; 87187</t>
+          <t>54557; 87362</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>113673; 164089</t>
+          <t>114140; 162553</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>70551; 109519</t>
+          <t>71741; 113052</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>166849; 1081122</t>
+          <t>168822; 1039504</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_psíq_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_psíq_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,59</t>
+          <t>0,27; 1,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,21</t>
+          <t>1,39; 4,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,07</t>
+          <t>0,43; 2,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,19</t>
+          <t>0,55; 2,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,29</t>
+          <t>0,14; 1,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,59</t>
+          <t>1,86; 4,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,21</t>
+          <t>0,55; 2,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,53</t>
+          <t>1,75; 3,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,07</t>
+          <t>0,28; 1,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,88</t>
+          <t>1,9; 3,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,81</t>
+          <t>0,66; 1,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,54</t>
+          <t>1,27; 2,5</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,19</t>
+          <t>0,63; 2,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,62</t>
+          <t>0,91; 2,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,32</t>
+          <t>0,61; 2,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,36</t>
+          <t>1,17; 3,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,02</t>
+          <t>0,6; 2,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,81</t>
+          <t>1,04; 2,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,71</t>
+          <t>0,94; 2,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,6</t>
+          <t>2,01; 3,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,81</t>
+          <t>0,73; 1,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,31</t>
+          <t>1,18; 2,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,06</t>
+          <t>0,96; 2,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,68</t>
+          <t>1,81; 3,04</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,53</t>
+          <t>0,15; 1,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,53</t>
+          <t>0,52; 2,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,48</t>
+          <t>0,14; 1,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,73</t>
+          <t>2,0; 4,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,18</t>
+          <t>0,93; 2,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,1</t>
+          <t>0,53; 2,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,15</t>
+          <t>0,52; 2,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 61,16</t>
+          <t>2,48; 5,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,03</t>
+          <t>0,71; 2,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,83</t>
+          <t>0,65; 1,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,53</t>
+          <t>0,46; 1,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 41,64</t>
+          <t>2,47; 4,42</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,97</t>
+          <t>0,46; 1,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,49</t>
+          <t>1,4; 3,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,44</t>
+          <t>0,4; 1,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,61</t>
+          <t>1,93; 4,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,02</t>
+          <t>0,64; 2,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,64</t>
+          <t>1,54; 3,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,46</t>
+          <t>1,46; 3,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,16</t>
+          <t>2,47; 4,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,69</t>
+          <t>0,71; 1,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,13</t>
+          <t>1,7; 3,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,25</t>
+          <t>1,05; 2,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,85</t>
+          <t>2,49; 3,9</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1277,32 +1277,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,31</t>
+          <t>0,63; 1,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,48</t>
+          <t>1,41; 2,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,36</t>
+          <t>0,64; 1,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,68</t>
+          <t>1,82; 2,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,6</t>
+          <t>0,84; 1,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,61</t>
+          <t>1,65; 2,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 25,12</t>
+          <t>2,6; 3,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,31</t>
+          <t>0,79; 1,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,33</t>
+          <t>1,65; 2,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,63</t>
+          <t>1,03; 1,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 14,49</t>
+          <t>2,34; 3,07</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17439</t>
+          <t>18963</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24693</t>
+          <t>26331</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1853; 11044</t>
+          <t>1897; 10861</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10579; 29592</t>
+          <t>9745; 29320</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3026; 13941</t>
+          <t>2884; 13947</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3689; 13945</t>
+          <t>3772; 14186</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>948; 8886</t>
+          <t>948; 8731</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13379; 32029</t>
+          <t>12996; 31898</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3697; 14883</t>
+          <t>3723; 15342</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11643; 25633</t>
+          <t>12872; 27426</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3785; 14739</t>
+          <t>3803; 15556</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27972; 54401</t>
+          <t>26666; 55161</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8458; 24410</t>
+          <t>8851; 25182</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18079; 34608</t>
+          <t>18109; 35620</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>19986</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26287</t>
+          <t>29737</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>43424</t>
+          <t>49724</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6101; 21018</t>
+          <t>6069; 22010</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9137; 26623</t>
+          <t>9261; 26496</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6205; 23771</t>
+          <t>6268; 22229</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8406; 28129</t>
+          <t>12272; 31515</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5528; 19579</t>
+          <t>5784; 20551</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10867; 28976</t>
+          <t>10687; 28058</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9391; 28299</t>
+          <t>9758; 26174</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19235; 34534</t>
+          <t>21568; 39803</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14317; 34870</t>
+          <t>14038; 34948</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23810; 47446</t>
+          <t>24106; 47667</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18902; 42576</t>
+          <t>19893; 43564</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28179; 57613</t>
+          <t>38366; 64526</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21645</t>
+          <t>24730</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>227057</t>
+          <t>28685</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>248702</t>
+          <t>53415</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>980; 10405</t>
+          <t>987; 10288</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3926; 19133</t>
+          <t>3927; 18475</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1409; 11241</t>
+          <t>1061; 11829</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13584; 33324</t>
+          <t>16053; 38028</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7213; 21765</t>
+          <t>6355; 20387</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4056; 16326</t>
+          <t>4087; 16340</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3129; 16846</t>
+          <t>4088; 16727</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23834; 570813</t>
+          <t>20131; 43305</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9836; 27629</t>
+          <t>9692; 27255</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10097; 28084</t>
+          <t>10046; 28131</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6790; 23656</t>
+          <t>7072; 22961</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44171; 682057</t>
+          <t>39975; 71367</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26949</t>
+          <t>29014</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>33445</t>
+          <t>36774</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>60394</t>
+          <t>65788</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4196; 18553</t>
+          <t>4287; 17949</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12952; 33119</t>
+          <t>13283; 32901</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2893; 13511</t>
+          <t>3750; 15035</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18158; 42702</t>
+          <t>19134; 43449</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6725; 21015</t>
+          <t>6659; 20873</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16837; 38240</t>
+          <t>16182; 37385</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15218; 36106</t>
+          <t>15196; 35929</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23956; 45527</t>
+          <t>27680; 47432</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14186; 33568</t>
+          <t>14090; 33729</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33902; 62505</t>
+          <t>34059; 62102</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21439; 44669</t>
+          <t>20795; 44105</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44668; 77759</t>
+          <t>52526; 82176</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72985</t>
+          <t>81098</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>304229</t>
+          <t>114160</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>377213</t>
+          <t>195258</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20150; 42995</t>
+          <t>20555; 44210</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>48781; 85110</t>
+          <t>48481; 83120</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21114; 46130</t>
+          <t>21819; 44714</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53415; 92622</t>
+          <t>64472; 102248</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>28386; 53962</t>
+          <t>28524; 55457</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>59306; 92986</t>
+          <t>58689; 93319</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42883; 74139</t>
+          <t>42859; 73940</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>99799; 932453</t>
+          <t>97053; 135221</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>54557; 87362</t>
+          <t>52846; 86909</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>114140; 162553</t>
+          <t>114989; 163756</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71741; 113052</t>
+          <t>71447; 109788</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>168822; 1039504</t>
+          <t>170301; 223138</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_psíq_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_psíq_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
